--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>102846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528167.0800516588</v>
+        <v>528167</v>
       </c>
       <c r="R2" t="n">
-        <v>6368780.674837141</v>
+        <v>6368781</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528167.0800516588</v>
+        <v>528167</v>
       </c>
       <c r="R3" t="n">
-        <v>6368780.674837141</v>
+        <v>6368781</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>104490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528167.0800516588</v>
+        <v>528167</v>
       </c>
       <c r="R4" t="n">
-        <v>6368780.674837141</v>
+        <v>6368781</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105218</v>
+        <v>105227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>106991</v>
+        <v>107000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105227</v>
+        <v>105230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107000</v>
+        <v>107005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105230</v>
+        <v>105258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107005</v>
+        <v>107033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105258</v>
+        <v>105264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107033</v>
+        <v>107039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105264</v>
+        <v>105271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107039</v>
+        <v>107046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105271</v>
+        <v>105275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107046</v>
+        <v>107050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105275</v>
+        <v>105282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107050</v>
+        <v>107058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105285</v>
+        <v>105290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107061</v>
+        <v>107066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105290</v>
+        <v>105298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107066</v>
+        <v>107074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19430-2025 artfynd.xlsx
+++ b/artfynd/A 19430-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74117272</v>
       </c>
       <c r="B2" t="n">
-        <v>105298</v>
+        <v>105308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74208579</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74553177</v>
       </c>
       <c r="B4" t="n">
-        <v>107074</v>
+        <v>107084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
